--- a/input/mapping/072. OCB_GOLD_TCKH_PST_ENTR_FCT_QUANG.xlsx
+++ b/input/mapping/072. OCB_GOLD_TCKH_PST_ENTR_FCT_QUANG.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30404"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="220" documentId="11_7A8BA08DDDE3F9AE523AB54160DAF33C22C13C69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CD39CA4-1C46-4D93-99A7-DE71570E0B88}"/>
+  <xr:revisionPtr revIDLastSave="223" documentId="11_7A8BA08DDDE3F9AE523AB54160DAF33C22C13C69" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A560C12-C26A-4A51-B9A2-190F3358BEAB}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -1242,12 +1242,11 @@
 ),</t>
   </si>
   <si>
-    <t>line_mv_hub AS (
-    SELECT line_movement_toanhang_hashkey        AS lm_hashkey,
-           max_by(t_line_id, source_event_date)  AS t_line_id
+    <t xml:space="preserve">line_mv_hub AS (
+    SELECT line_movement_toanhang_hashkey AS lm_hashkey,
+           t_line_id
     FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_line_movement_toanhang')
     WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
-    GROUP BY line_movement_toanhang_hashkey
 ),
 line_mv AS (
     SELECT lm_hashkey, t_line_id FROM line_mv_hub
@@ -1695,7 +1694,8 @@
               AND g.AUTO_DIM_ID = 0 THEN g.OU_DW_ID_COM
          ELSE NULL END                                              AS OU_ID_CREATED_COM
 FROM   flg g
-       LEFT JOIN branch_active hbu ON hbu.business_key = g.t_comp_report;</t>
+       LEFT JOIN branch_active hbu ON hbu.business_key = g.t_comp_report;
+</t>
   </si>
 </sst>
 </file>
@@ -1983,7 +1983,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2061,11 +2061,75 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2079,75 +2143,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2489,657 +2485,656 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3F26D1-52C0-4A13-896C-D099FB00DA50}">
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="8" width="25.42578125" style="56" customWidth="1"/>
+    <col min="6" max="8" width="25.42578125" style="35" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1">
-      <c r="A3" s="36"/>
-      <c r="B3" s="53" t="s">
+      <c r="A3" s="13"/>
+      <c r="B3" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="58" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="K3" s="54"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1">
-      <c r="A4" s="36"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="K4" s="54"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1">
-      <c r="A5" s="36"/>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="K5" s="54"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="15" customHeight="1">
-      <c r="A6" s="36"/>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="K6" s="54"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="K6" s="33"/>
     </row>
     <row r="7" spans="1:11" ht="15" customHeight="1">
-      <c r="A7" s="36"/>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="K7" s="54"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="K7" s="33"/>
     </row>
     <row r="8" spans="1:11" ht="15" customHeight="1">
-      <c r="A8" s="36"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="37" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
     </row>
     <row r="10" spans="1:11" ht="15" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1">
-      <c r="A12" s="36"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
+      <c r="A12" s="13"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
+      <c r="A13" s="13"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1">
-      <c r="A14" s="36"/>
-      <c r="B14" s="53"/>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
     </row>
     <row r="15" spans="1:11" ht="15" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
     </row>
     <row r="16" spans="1:11" ht="15" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-    </row>
-    <row r="17" spans="1:13" ht="15" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1">
-      <c r="A18" s="36"/>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="37" t="s">
+      <c r="A16" s="13"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1">
+      <c r="A17" s="13"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="40"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1">
+      <c r="A18" s="13"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-    </row>
-    <row r="19" spans="1:13" ht="15" customHeight="1">
-      <c r="A19" s="36"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-    </row>
-    <row r="20" spans="1:13" ht="15" customHeight="1">
-      <c r="A20" s="36"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-    </row>
-    <row r="21" spans="1:13" ht="15" customHeight="1">
-      <c r="A21" s="36"/>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1">
-      <c r="A22" s="36"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-    </row>
-    <row r="23" spans="1:13" ht="15" customHeight="1">
-      <c r="A23" s="36"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-    </row>
-    <row r="24" spans="1:13" ht="15" customHeight="1">
-      <c r="A24" s="36"/>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-    </row>
-    <row r="25" spans="1:13" ht="15" customHeight="1">
-      <c r="A25" s="36"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-    </row>
-    <row r="26" spans="1:13" ht="15" customHeight="1">
-      <c r="A26" s="36"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-    </row>
-    <row r="27" spans="1:13" ht="15" customHeight="1">
-      <c r="A27" s="36"/>
-      <c r="B27" s="53"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="37" t="s">
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="40"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1">
+      <c r="A19" s="13"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1">
+      <c r="A20" s="13"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1">
+      <c r="A21" s="13"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="40"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1">
+      <c r="A22" s="13"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="40"/>
+      <c r="H22" s="40"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1">
+      <c r="A23" s="13"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="40"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1">
+      <c r="A24" s="13"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1">
+      <c r="A25" s="13"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="40"/>
+      <c r="G25" s="40"/>
+      <c r="H25" s="40"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1">
+      <c r="A26" s="13"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="40"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1">
+      <c r="A27" s="13"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-    </row>
-    <row r="28" spans="1:13" ht="15" customHeight="1">
-      <c r="A28" s="36"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="53"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-    </row>
-    <row r="29" spans="1:13" ht="15" customHeight="1">
-      <c r="A29" s="36"/>
-      <c r="B29" s="53"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="M29" s="57"/>
-    </row>
-    <row r="30" spans="1:13" ht="15" customHeight="1">
-      <c r="A30" s="36"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-    </row>
-    <row r="31" spans="1:13" ht="15" customHeight="1">
-      <c r="A31" s="36"/>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-    </row>
-    <row r="32" spans="1:13" ht="15" customHeight="1">
-      <c r="A32" s="36"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="40"/>
+      <c r="H27" s="40"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1">
+      <c r="A28" s="13"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="40"/>
+      <c r="H28" s="40"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1">
+      <c r="A29" s="13"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1">
+      <c r="A30" s="13"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="40"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1">
+      <c r="A31" s="13"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1">
+      <c r="A32" s="13"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="40"/>
+      <c r="H32" s="40"/>
     </row>
     <row r="33" spans="1:8" ht="15" customHeight="1">
-      <c r="A33" s="36"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
+      <c r="A33" s="13"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="40"/>
+      <c r="H33" s="40"/>
     </row>
     <row r="34" spans="1:8" ht="15" customHeight="1">
-      <c r="A34" s="36"/>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
+      <c r="A34" s="13"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1">
-      <c r="A35" s="36"/>
-      <c r="B35" s="53"/>
-      <c r="C35" s="53"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1">
-      <c r="A36" s="36"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="37" t="s">
+      <c r="A36" s="13"/>
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="40"/>
+      <c r="H36" s="40"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1">
-      <c r="A37" s="36"/>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
+      <c r="A37" s="13"/>
+      <c r="B37" s="39"/>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
+      <c r="H37" s="40"/>
     </row>
     <row r="38" spans="1:8" ht="15" customHeight="1">
-      <c r="A38" s="36"/>
-      <c r="B38" s="53"/>
-      <c r="C38" s="53"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
+      <c r="A38" s="13"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="40"/>
+      <c r="H38" s="40"/>
     </row>
     <row r="39" spans="1:8" ht="15" customHeight="1">
-      <c r="A39" s="36"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
+      <c r="A39" s="13"/>
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
     </row>
     <row r="40" spans="1:8" ht="15" customHeight="1">
-      <c r="A40" s="36"/>
-      <c r="B40" s="53"/>
-      <c r="C40" s="53"/>
-      <c r="D40" s="53"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
+      <c r="A40" s="13"/>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="39"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1">
-      <c r="A41" s="36"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
+      <c r="A41" s="13"/>
+      <c r="B41" s="39"/>
+      <c r="C41" s="39"/>
+      <c r="D41" s="39"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="40"/>
+      <c r="H41" s="40"/>
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1">
-      <c r="A42" s="36"/>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
+      <c r="A42" s="13"/>
+      <c r="B42" s="39"/>
+      <c r="C42" s="39"/>
+      <c r="D42" s="39"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="40"/>
+      <c r="H42" s="40"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1">
-      <c r="A43" s="36"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="53"/>
-      <c r="D43" s="53"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
+      <c r="A43" s="13"/>
+      <c r="B43" s="39"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="39"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1">
-      <c r="A44" s="36"/>
-      <c r="B44" s="53"/>
-      <c r="C44" s="53"/>
-      <c r="D44" s="53"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
+      <c r="A44" s="13"/>
+      <c r="B44" s="39"/>
+      <c r="C44" s="39"/>
+      <c r="D44" s="39"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="40"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1">
-      <c r="A45" s="36"/>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="36"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
+      <c r="A45" s="13"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1">
-      <c r="A46" s="36"/>
-      <c r="B46" s="53"/>
-      <c r="C46" s="53"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
+      <c r="A46" s="13"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="40"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1">
-      <c r="A47" s="36"/>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="37" t="s">
+      <c r="A47" s="13"/>
+      <c r="B47" s="39"/>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+      <c r="E47" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1">
-      <c r="A48" s="36"/>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="36"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
+      <c r="A48" s="13"/>
+      <c r="B48" s="39"/>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1">
-      <c r="A49" s="36"/>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="36"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
+      <c r="A49" s="13"/>
+      <c r="B49" s="39"/>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
     </row>
     <row r="50" spans="1:9" ht="15" customHeight="1">
-      <c r="A50" s="36"/>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
+      <c r="A50" s="13"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1">
-      <c r="A51" s="36"/>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="36"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
+      <c r="A51" s="13"/>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
     </row>
     <row r="52" spans="1:9" ht="15" customHeight="1">
-      <c r="A52" s="36"/>
-      <c r="B52" s="53"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="36"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
+      <c r="A52" s="13"/>
+      <c r="B52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40"/>
+      <c r="H52" s="40"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="36"/>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
+      <c r="A53" s="13"/>
+      <c r="B53" s="39"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40"/>
+      <c r="H53" s="40"/>
     </row>
     <row r="55" spans="1:9" ht="15.75">
-      <c r="B55" s="38" t="s">
+      <c r="B55" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="39"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="31"/>
     </row>
     <row r="56" spans="1:9">
-      <c r="B56" s="43"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="40" t="s">
+      <c r="B56" s="41"/>
+      <c r="C56" s="42"/>
+      <c r="D56" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="43"/>
+      <c r="H56" s="43"/>
+      <c r="I56" s="43"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="B57" s="45"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="40" t="s">
+      <c r="B57" s="44"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="41"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="46"/>
     </row>
     <row r="58" spans="1:9">
-      <c r="B58" s="47"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="40" t="s">
+      <c r="B58" s="51"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="43"/>
+      <c r="I58" s="43"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="B59" s="49"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="40" t="s">
+      <c r="B59" s="47"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="40"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="43"/>
+      <c r="I59" s="43"/>
     </row>
     <row r="60" spans="1:9">
-      <c r="B60" s="51"/>
-      <c r="C60" s="52"/>
-      <c r="D60" s="40" t="s">
+      <c r="B60" s="49"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="43"/>
+      <c r="H60" s="43"/>
+      <c r="I60" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:I57"/>
     <mergeCell ref="D58:I58"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="D59:I59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:I60"/>
+    <mergeCell ref="A1:K1"/>
     <mergeCell ref="B3:D53"/>
     <mergeCell ref="F3:H53"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="D56:I56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:I57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3159,15 +3154,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="6" t="s">
@@ -3193,15 +3188,15 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="8">
@@ -3480,15 +3475,15 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33" t="s">
+      <c r="A16" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="34"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="56"/>
     </row>
     <row r="17" spans="1:7" ht="72">
       <c r="A17" s="21">
@@ -3560,15 +3555,15 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="34"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="56"/>
     </row>
     <row r="21" spans="1:7" ht="115.5">
       <c r="A21" s="21">
@@ -3636,15 +3631,15 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="34"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="56"/>
     </row>
     <row r="25" spans="1:7" ht="43.5">
       <c r="A25" s="21">
@@ -3961,15 +3956,15 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="6" t="s">
@@ -4603,36 +4598,36 @@
       <c r="C1" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
     </row>
     <row r="2" spans="1:31" ht="33.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -4662,14 +4657,14 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="409.6">
+    <row r="4" spans="1:31">
       <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="57" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4829,15 +4824,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
@@ -4847,7 +4833,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -5019,14 +5005,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{770772BE-08BF-4FD4-A7E3-7AEFA1064A07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10E9342E-E0CD-4A5B-8799-461EDCE94F8A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10E9342E-E0CD-4A5B-8799-461EDCE94F8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D19129E7-BC70-4266-861D-8766315B7EF1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D19129E7-BC70-4266-861D-8766315B7EF1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{770772BE-08BF-4FD4-A7E3-7AEFA1064A07}"/>
 </file>